--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Asset Allocator Fund (FOF).xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Asset Allocator Fund (FOF).xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="80">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Asset Allocator Fund (FOF)</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -70,6 +70,12 @@
     <t>INF109K013J1</t>
   </si>
   <si>
+    <t>ICICI Prudential Technology Fund - Direct - Growth</t>
+  </si>
+  <si>
+    <t>INF109K01Z48</t>
+  </si>
+  <si>
     <t>ICICI Prudential Short Term Fund - Direct Plan -  Growth Option</t>
   </si>
   <si>
@@ -82,52 +88,64 @@
     <t>INF109K018M4</t>
   </si>
   <si>
+    <t>ICICI Prudential Energy Opportunities Fund - Direct - Growth</t>
+  </si>
+  <si>
+    <t>INF109KC12W6</t>
+  </si>
+  <si>
+    <t>ICICI Prudential Focused Equity Fund - Direct - Growth</t>
+  </si>
+  <si>
+    <t>INF109K018N2</t>
+  </si>
+  <si>
+    <t>ICICI Prudential Large &amp; Mid Cap Fund - Direct Plan - Growth</t>
+  </si>
+  <si>
+    <t>INF109K011O5</t>
+  </si>
+  <si>
+    <t>ICICI Prudential Innovation Fund - Direct Plan - Growth</t>
+  </si>
+  <si>
+    <t>INF109KC12T2</t>
+  </si>
+  <si>
     <t>ICICI Prudential Savings Fund - Direct - Growth</t>
   </si>
   <si>
     <t>INF109K01O82</t>
   </si>
   <si>
-    <t>ICICI Prudential Technology Fund - Direct - Growth</t>
-  </si>
-  <si>
-    <t>INF109K01Z48</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Focused Equity Fund - Direct - Growth</t>
-  </si>
-  <si>
-    <t>INF109K018N2</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Innovation Fund - Direct Plan - Growth</t>
-  </si>
-  <si>
-    <t>INF109KC12T2</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Gold ETF</t>
-  </si>
-  <si>
-    <t>INF109KC1NT3</t>
-  </si>
-  <si>
     <t>ICICI Prudential Banking &amp; PSU Debt Fund - Direct Plan - Growth</t>
   </si>
   <si>
     <t>INF109K010A6</t>
   </si>
   <si>
-    <t>ICICI Prudential Large &amp; Mid Cap Fund - Direct Plan - Growth</t>
-  </si>
-  <si>
-    <t>INF109K011O5</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Energy Opportunities Fund - Direct - Growth</t>
-  </si>
-  <si>
-    <t>INF109KC12W6</t>
+    <t>ICICI Prudential Gilt Fund - Direct Plan - Growth</t>
+  </si>
+  <si>
+    <t>INF109K018C5</t>
+  </si>
+  <si>
+    <t>ICICI Prudential Equity Minimum Variance Fund - Direct - Growth</t>
+  </si>
+  <si>
+    <t>INF109KC10Y6</t>
+  </si>
+  <si>
+    <t>ICICI Prudential Corporate Bond Fund- Direct Plan -  Growth</t>
+  </si>
+  <si>
+    <t>INF109K016B1</t>
+  </si>
+  <si>
+    <t>ICICI Prudential Pharma Healthcare and Diagnostics (P.H.D) Fund - Direct Plan - Growth</t>
+  </si>
+  <si>
+    <t>INF109KC1GH2</t>
   </si>
   <si>
     <t>ICICI Prudential Floating Interest Fund - Direct Plan</t>
@@ -136,30 +154,12 @@
     <t>INF109K01P57</t>
   </si>
   <si>
-    <t>ICICI Prudential Equity Minimum Variance Fund - Direct - Growth</t>
-  </si>
-  <si>
-    <t>INF109KC10Y6</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Corporate Bond Fund- Direct Plan -  Growth</t>
-  </si>
-  <si>
-    <t>INF109K016B1</t>
-  </si>
-  <si>
     <t>ICICI Prudential Bharat Consumption Fund - Direct - Growth</t>
   </si>
   <si>
     <t>INF109KC1YD4</t>
   </si>
   <si>
-    <t>ICICI Prudential Gilt Fund - Direct Plan - Growth</t>
-  </si>
-  <si>
-    <t>INF109K018C5</t>
-  </si>
-  <si>
     <t>ICICI Prudential Commodities Fund - Direct - Growth</t>
   </si>
   <si>
@@ -172,10 +172,16 @@
     <t>INF109K01V83</t>
   </si>
   <si>
-    <t>ICICI Prudential Pharma Healthcare and Diagnostics (P.H.D) Fund - Direct Plan - Growth</t>
-  </si>
-  <si>
-    <t>INF109KC1GH2</t>
+    <t>ICICI Prudential Medium Term Bond Fund - Direct Plan - Growth</t>
+  </si>
+  <si>
+    <t>INF109K015A5</t>
+  </si>
+  <si>
+    <t>ICICI Prudential Ultra Short Term Fund - Direct Plan - Growth</t>
+  </si>
+  <si>
+    <t>INF109K01T04</t>
   </si>
   <si>
     <t>ICICI Prudential FMCG Fund - Direct Plan - Growth</t>
@@ -184,10 +190,10 @@
     <t>INF109K01Z14</t>
   </si>
   <si>
-    <t>ICICI Prudential Medium Term Bond Fund - Direct Plan - Growth</t>
-  </si>
-  <si>
-    <t>INF109K015A5</t>
+    <t>ICICI Prudential Transportation &amp; Logistic Fund - Direct - Growth</t>
+  </si>
+  <si>
+    <t>INF109KC12K1</t>
   </si>
   <si>
     <t>ICICI Prudential Exports and Services Fund - Direct - Growth</t>
@@ -196,10 +202,10 @@
     <t>INF109K01W25</t>
   </si>
   <si>
-    <t>ICICI Prudential Transportation &amp; Logistic Fund - Direct - Growth</t>
-  </si>
-  <si>
-    <t>INF109KC12K1</t>
+    <t>ICICI Prudential Money Market fund - Direct Plan -  Growth Option</t>
+  </si>
+  <si>
+    <t>INF109K01R14</t>
   </si>
   <si>
     <t>ICICI Prudential Credit Risk Fund - Direct Plan - Growth</t>
@@ -208,6 +214,12 @@
     <t>INF109K01V00</t>
   </si>
   <si>
+    <t>ICICI Prudential Housing Opportunities Fund - Direct - Growth</t>
+  </si>
+  <si>
+    <t>INF109KC10C2</t>
+  </si>
+  <si>
     <t>ICICI Prudential Quant Fund - Direct - Growth</t>
   </si>
   <si>
@@ -229,7 +241,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -544,13 +556,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -568,7 +580,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="9410700"/>
+          <a:off x="666750" y="9791700"/>
           <a:ext cx="6019800" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -583,13 +595,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -607,7 +619,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="12268200"/>
+          <a:off x="666750" y="12649200"/>
           <a:ext cx="6019800" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -941,7 +953,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J61"/>
+  <dimension ref="B1:J63"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
@@ -1035,10 +1047,10 @@
         <v>12</v>
       </c>
       <c r="F5" s="9">
-        <v>2346881.18</v>
+        <v>2509793.78</v>
       </c>
       <c r="G5" s="10">
-        <v>0.9838401805995</v>
+        <v>0.9626935177655</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>12</v>
@@ -1058,13 +1070,13 @@
         <v>15</v>
       </c>
       <c r="E6" s="14">
-        <v>754316852.132</v>
+        <v>858143680.743</v>
       </c>
       <c r="F6" s="15">
-        <v>288895.06</v>
+        <v>343258.33</v>
       </c>
       <c r="G6" s="16">
-        <v>0.1211082054034</v>
+        <v>0.1316652275751</v>
       </c>
       <c r="H6" s="15" t="s">
         <v>12</v>
@@ -1084,13 +1096,13 @@
         <v>15</v>
       </c>
       <c r="E7" s="14">
-        <v>151219737.327</v>
+        <v>115028218.633</v>
       </c>
       <c r="F7" s="15">
-        <v>201394.45</v>
+        <v>172036.20</v>
       </c>
       <c r="G7" s="16">
-        <v>0.0844269210339</v>
+        <v>0.0659887421353</v>
       </c>
       <c r="H7" s="15" t="s">
         <v>12</v>
@@ -1110,13 +1122,13 @@
         <v>15</v>
       </c>
       <c r="E8" s="14">
-        <v>262025064.538</v>
+        <v>76863890.859</v>
       </c>
       <c r="F8" s="15">
-        <v>165008.45</v>
+        <v>168347.29</v>
       </c>
       <c r="G8" s="16">
-        <v>0.06917348208</v>
+        <v>0.06457376941</v>
       </c>
       <c r="H8" s="15" t="s">
         <v>12</v>
@@ -1136,13 +1148,13 @@
         <v>15</v>
       </c>
       <c r="E9" s="14">
-        <v>81793935.957</v>
+        <v>254324855.246</v>
       </c>
       <c r="F9" s="15">
-        <v>158475.75</v>
+        <v>166694.94</v>
       </c>
       <c r="G9" s="16">
-        <v>0.0664348974415</v>
+        <v>0.0639399696745</v>
       </c>
       <c r="H9" s="15" t="s">
         <v>12</v>
@@ -1162,13 +1174,13 @@
         <v>15</v>
       </c>
       <c r="E10" s="14">
-        <v>27452675.163</v>
+        <v>78002507.584</v>
       </c>
       <c r="F10" s="15">
-        <v>146021.19</v>
+        <v>163181.25</v>
       </c>
       <c r="G10" s="16">
-        <v>0.0612137994737</v>
+        <v>0.0625922069167</v>
       </c>
       <c r="H10" s="15" t="s">
         <v>12</v>
@@ -1188,13 +1200,13 @@
         <v>15</v>
       </c>
       <c r="E11" s="14">
-        <v>55914056.186</v>
+        <v>1299555518.816</v>
       </c>
       <c r="F11" s="15">
-        <v>129961.04</v>
+        <v>131904.89</v>
       </c>
       <c r="G11" s="16">
-        <v>0.0544811957905</v>
+        <v>0.050595384998</v>
       </c>
       <c r="H11" s="15" t="s">
         <v>12</v>
@@ -1214,13 +1226,13 @@
         <v>15</v>
       </c>
       <c r="E12" s="14">
-        <v>126175849.214</v>
+        <v>124471895.947</v>
       </c>
       <c r="F12" s="15">
-        <v>118264.62</v>
+        <v>127633.48</v>
       </c>
       <c r="G12" s="16">
-        <v>0.0495779190233</v>
+        <v>0.0489569799818</v>
       </c>
       <c r="H12" s="15" t="s">
         <v>12</v>
@@ -1240,13 +1252,13 @@
         <v>15</v>
       </c>
       <c r="E13" s="14">
-        <v>667022313.64</v>
+        <v>11298052.819</v>
       </c>
       <c r="F13" s="15">
-        <v>116462.10</v>
+        <v>124594.93</v>
       </c>
       <c r="G13" s="16">
-        <v>0.0488222814489</v>
+        <v>0.04779146893</v>
       </c>
       <c r="H13" s="15" t="s">
         <v>12</v>
@@ -1266,13 +1278,13 @@
         <v>15</v>
       </c>
       <c r="E14" s="14">
-        <v>161707620</v>
+        <v>638788584.542</v>
       </c>
       <c r="F14" s="15">
-        <v>115265.19</v>
+        <v>117217.71</v>
       </c>
       <c r="G14" s="16">
-        <v>0.048320522706</v>
+        <v>0.0449617536244</v>
       </c>
       <c r="H14" s="15" t="s">
         <v>12</v>
@@ -1292,13 +1304,13 @@
         <v>15</v>
       </c>
       <c r="E15" s="14">
-        <v>307857484.895</v>
+        <v>18953614.183</v>
       </c>
       <c r="F15" s="15">
-        <v>101053.60</v>
+        <v>104060.65</v>
       </c>
       <c r="G15" s="16">
-        <v>0.0423628571065</v>
+        <v>0.0399150376448</v>
       </c>
       <c r="H15" s="15" t="s">
         <v>12</v>
@@ -1318,13 +1330,13 @@
         <v>15</v>
       </c>
       <c r="E16" s="14">
-        <v>9255460.349</v>
+        <v>270698888.817</v>
       </c>
       <c r="F16" s="15">
-        <v>95472.85</v>
+        <v>92458.56</v>
       </c>
       <c r="G16" s="16">
-        <v>0.0400233410992</v>
+        <v>0.0354647688919</v>
       </c>
       <c r="H16" s="15" t="s">
         <v>12</v>
@@ -1344,13 +1356,13 @@
         <v>15</v>
       </c>
       <c r="E17" s="14">
-        <v>1011487529.098</v>
+        <v>79510903.918</v>
       </c>
       <c r="F17" s="15">
-        <v>94574.08</v>
+        <v>88636.45</v>
       </c>
       <c r="G17" s="16">
-        <v>0.0396465661492</v>
+        <v>0.0339987040102</v>
       </c>
       <c r="H17" s="15" t="s">
         <v>12</v>
@@ -1370,13 +1382,13 @@
         <v>15</v>
       </c>
       <c r="E18" s="14">
-        <v>17223752.9</v>
+        <v>792015067.789</v>
       </c>
       <c r="F18" s="15">
-        <v>76788.71</v>
+        <v>82765.57</v>
       </c>
       <c r="G18" s="16">
-        <v>0.0321907299603</v>
+        <v>0.0317467826911</v>
       </c>
       <c r="H18" s="15" t="s">
         <v>12</v>
@@ -1396,13 +1408,13 @@
         <v>15</v>
       </c>
       <c r="E19" s="14">
-        <v>765672865.405</v>
+        <v>261806499.466</v>
       </c>
       <c r="F19" s="15">
-        <v>75495.34</v>
+        <v>81818.72</v>
       </c>
       <c r="G19" s="16">
-        <v>0.0316485340515</v>
+        <v>0.0313835949406</v>
       </c>
       <c r="H19" s="15" t="s">
         <v>12</v>
@@ -1422,13 +1434,13 @@
         <v>15</v>
       </c>
       <c r="E20" s="14">
-        <v>245857409.091</v>
+        <v>189015407.201</v>
       </c>
       <c r="F20" s="15">
-        <v>73847.70</v>
+        <v>78384.69</v>
       </c>
       <c r="G20" s="16">
-        <v>0.0309578239938</v>
+        <v>0.0300663877472</v>
       </c>
       <c r="H20" s="15" t="s">
         <v>12</v>
@@ -1448,13 +1460,13 @@
         <v>15</v>
       </c>
       <c r="E21" s="14">
-        <v>212533173.958</v>
+        <v>16691416.699</v>
       </c>
       <c r="F21" s="15">
-        <v>54961.08</v>
+        <v>77052.35</v>
       </c>
       <c r="G21" s="16">
-        <v>0.0230403308586</v>
+        <v>0.0295553357669</v>
       </c>
       <c r="H21" s="15" t="s">
         <v>12</v>
@@ -1474,13 +1486,13 @@
         <v>15</v>
       </c>
       <c r="E22" s="14">
-        <v>51395805.741</v>
+        <v>212533173.958</v>
       </c>
       <c r="F22" s="15">
-        <v>54560.66</v>
+        <v>56193.77</v>
       </c>
       <c r="G22" s="16">
-        <v>0.0228724700873</v>
+        <v>0.0215545111909</v>
       </c>
       <c r="H22" s="15" t="s">
         <v>12</v>
@@ -1500,13 +1512,13 @@
         <v>15</v>
       </c>
       <c r="E23" s="14">
-        <v>116822760.288</v>
+        <v>124595545.645</v>
       </c>
       <c r="F23" s="15">
-        <v>47394.99</v>
+        <v>53850.19</v>
       </c>
       <c r="G23" s="16">
-        <v>0.0198685369836</v>
+        <v>0.0206555730819</v>
       </c>
       <c r="H23" s="15" t="s">
         <v>12</v>
@@ -1529,10 +1541,10 @@
         <v>113486330.782</v>
       </c>
       <c r="F24" s="15">
-        <v>46409.78</v>
+        <v>48668.27</v>
       </c>
       <c r="G24" s="16">
-        <v>0.0194555253695</v>
+        <v>0.0186679194216</v>
       </c>
       <c r="H24" s="15" t="s">
         <v>12</v>
@@ -1552,13 +1564,13 @@
         <v>15</v>
       </c>
       <c r="E25" s="14">
-        <v>100153027.074</v>
+        <v>81861202.271</v>
       </c>
       <c r="F25" s="15">
-        <v>39910.98</v>
+        <v>40232.98</v>
       </c>
       <c r="G25" s="16">
-        <v>0.0167311520096</v>
+        <v>0.0154323551819</v>
       </c>
       <c r="H25" s="15" t="s">
         <v>12</v>
@@ -1578,13 +1590,13 @@
         <v>15</v>
       </c>
       <c r="E26" s="14">
-        <v>7404676.667</v>
+        <v>134670091.975</v>
       </c>
       <c r="F26" s="15">
-        <v>39046.34</v>
+        <v>40123.88</v>
       </c>
       <c r="G26" s="16">
-        <v>0.0163686847569</v>
+        <v>0.0153905071769</v>
       </c>
       <c r="H26" s="15" t="s">
         <v>12</v>
@@ -1604,13 +1616,13 @@
         <v>15</v>
       </c>
       <c r="E27" s="14">
-        <v>81861202.271</v>
+        <v>7404676.667</v>
       </c>
       <c r="F27" s="15">
-        <v>38639.55</v>
+        <v>38856.78</v>
       </c>
       <c r="G27" s="16">
-        <v>0.0161981536067</v>
+        <v>0.0149044796131</v>
       </c>
       <c r="H27" s="15" t="s">
         <v>12</v>
@@ -1630,13 +1642,13 @@
         <v>15</v>
       </c>
       <c r="E28" s="14">
-        <v>18823926.369</v>
+        <v>207082739.665</v>
       </c>
       <c r="F28" s="15">
-        <v>30993.59</v>
+        <v>38496.68</v>
       </c>
       <c r="G28" s="16">
-        <v>0.0129928772887</v>
+        <v>0.0147663543462</v>
       </c>
       <c r="H28" s="15" t="s">
         <v>12</v>
@@ -1656,13 +1668,13 @@
         <v>15</v>
       </c>
       <c r="E29" s="14">
-        <v>144813920.182</v>
+        <v>16355809.647</v>
       </c>
       <c r="F29" s="15">
-        <v>25820.32</v>
+        <v>28962.87</v>
       </c>
       <c r="G29" s="16">
-        <v>0.0108241816877</v>
+        <v>0.0111094255739</v>
       </c>
       <c r="H29" s="15" t="s">
         <v>12</v>
@@ -1682,13 +1694,13 @@
         <v>15</v>
       </c>
       <c r="E30" s="14">
-        <v>30246521.552</v>
+        <v>5339746.709</v>
       </c>
       <c r="F30" s="15">
-        <v>10152.94</v>
+        <v>20429.33</v>
       </c>
       <c r="G30" s="16">
-        <v>0.004256231806</v>
+        <v>0.0078361751152</v>
       </c>
       <c r="H30" s="15" t="s">
         <v>12</v>
@@ -1708,13 +1720,13 @@
         <v>15</v>
       </c>
       <c r="E31" s="14">
-        <v>9102867.569</v>
+        <v>30246521.552</v>
       </c>
       <c r="F31" s="15">
-        <v>2010.82</v>
+        <v>10550.44</v>
       </c>
       <c r="G31" s="16">
-        <v>0.0008429593832</v>
+        <v>0.0040468823687</v>
       </c>
       <c r="H31" s="15" t="s">
         <v>12</v>
@@ -1725,6 +1737,24 @@
     </row>
     <row r="32" spans="2:9" ht="15" customHeight="1">
       <c r="B32" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" s="14">
+        <v>59769874.626</v>
+      </c>
+      <c r="F32" s="15">
+        <v>10525.47</v>
+      </c>
+      <c r="G32" s="16">
+        <v>0.0040373045073</v>
+      </c>
+      <c r="H32" s="15" t="s">
         <v>12</v>
       </c>
       <c r="I32" s="11" t="s">
@@ -1732,25 +1762,25 @@
       </c>
     </row>
     <row r="33" spans="2:9" ht="15" customHeight="1">
-      <c r="B33" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" s="9">
-        <v>43335.96</v>
-      </c>
-      <c r="G33" s="10">
-        <v>0.0181669438897</v>
-      </c>
-      <c r="H33" s="9" t="s">
+      <c r="B33" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" s="14">
+        <v>12395271.152</v>
+      </c>
+      <c r="F33" s="15">
+        <v>2857.11</v>
+      </c>
+      <c r="G33" s="16">
+        <v>0.0010959152494</v>
+      </c>
+      <c r="H33" s="15" t="s">
         <v>12</v>
       </c>
       <c r="I33" s="11" t="s">
@@ -1766,90 +1796,124 @@
       </c>
     </row>
     <row r="35" spans="2:9" ht="15" customHeight="1">
-      <c r="B35" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C35" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="D35" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="E35" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" s="18">
-        <v>-4787.853540959302</v>
-      </c>
-      <c r="G35" s="19">
-        <v>-0.0020071244903957937</v>
-      </c>
-      <c r="H35" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="I35" s="6" t="s">
+      <c r="B35" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="9">
+        <v>99962.14</v>
+      </c>
+      <c r="G35" s="10">
+        <v>0.0383429527027</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I35" s="11" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="36" spans="2:9" ht="15" customHeight="1">
-      <c r="B36" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="C36" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="D36" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="E36" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="F36" s="18">
-        <v>2385429.28645904</v>
-      </c>
-      <c r="G36" s="19">
-        <v>0.9999999999988043</v>
-      </c>
-      <c r="H36" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="B39" s="13" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="40" ht="27.5" customHeight="1">
-      <c r="B40" s="20" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="41" ht="27.5" customHeight="1">
-      <c r="B41" s="20" t="s">
+      <c r="B36" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" ht="15" customHeight="1">
+      <c r="B37" s="17" t="s">
         <v>71</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" s="18">
+        <v>-2702.134261369705</v>
+      </c>
+      <c r="G37" s="19">
+        <v>-0.001036470469520496</v>
+      </c>
+      <c r="H37" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" ht="15" customHeight="1">
+      <c r="B38" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="18">
+        <v>2607053.78573863</v>
+      </c>
+      <c r="G38" s="19">
+        <v>0.9999999999986796</v>
+      </c>
+      <c r="H38" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="B41" s="13" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="42" ht="27.5" customHeight="1">
       <c r="B42" s="20" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="45" ht="15">
-      <c r="B45" s="21" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="60" ht="15">
-      <c r="B60" s="21" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="61" ht="15">
-      <c r="B61" s="21" t="s">
+    <row r="43" ht="27.5" customHeight="1">
+      <c r="B43" s="20" t="s">
         <v>75</v>
+      </c>
+    </row>
+    <row r="44" ht="27.5" customHeight="1">
+      <c r="B44" s="20" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="47" ht="15">
+      <c r="B47" s="21" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="62" ht="15">
+      <c r="B62" s="21" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="63" ht="15">
+      <c r="B63" s="21" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1857,10 +1921,10 @@
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B40:H40"/>
     <mergeCell ref="B41:H41"/>
     <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="B44:H44"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
